--- a/ig/carecommunication/all-profiles.xlsx
+++ b/ig/carecommunication/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.1</t>
+    <t>5.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T10:10:10+00:00</t>
+    <t>2026-02-13T11:55:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1587,7 +1587,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}medcom-messaging-1:The MessageHeader resource shall conform to medcom-messaging-messageHeader profile {entry[0].resource.conformsTo('http://medcomfhir.dk/ig/messaging/StructureDefinition/medcom-messaging-messageHeader')}medcom-messaging-2:There shall be at least one Provenance resource in a MedCom message {entry.resource.ofType(Provenance).exists()}medcom-careCommunication-1:The MessageHeader shall conform to medcom-careCommunication-messageHeader profile {entry[0].resource.conformsTo('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-messageHeader')}medcom-careCommunication-2:Entry shall contain exactly one Patient resource {entry.where(resource.is(Patient)).count() = 1}medcom-careCommunication-4:There shall exist a practitioner given and family name when using a PractitionerRole. {entry.resource.ofType(Practitioner).name.exists()}medcom-careCommunication-3:All Provenance resources shall be of the type medcom-careCommunication-provenance profile {entry.resource.ofType(Provenance).all(conformsTo('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-provenance'))}medcom-careCommunication-12:If a specific recipient is present, at least one of the organisations that the referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.receiver.
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}medcom-messaging-2:There shall be at least one Provenance resource in a MedCom message {entry.resource.ofType(Provenance).exists()}medcom-careCommunication-1:The MessageHeader shall be the medcom-careCommunication-messageHeader {entry[0].resource.ofType(MessageHeader).meta.profile.startsWith('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-messageHeader')}medcom-careCommunication-2:Entry shall contain exactly one Patient resource {entry.where(resource.is(Patient)).count() = 1}medcom-careCommunication-4:There shall exist a practitioner given and family name when using a PractitionerRole. {entry.resource.ofType(Practitioner).name.exists()}medcom-careCommunication-3:All Provenance resources shall be of the type medcom-careCommunication-provenance profile {entry.resource.ofType(Provenance).all(meta.profile.startsWith('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-provenance'))}medcom-careCommunication-12:If a specific recipient is present, at least one of the organisations that the referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.receiver.
 If no specific recipient is present, this rule is not evaluated. {Bundle.entry.resource.ofType(Communication).recipient.reference.resolve().managingOrganization.reference.resolve() = %resource.entry.resource.ofType(MessageHeader).destination.receiver.reference.resolve() or Bundle.entry.resource.ofType(Communication).recipient.reference.resolve().organization.reference.resolve() = %resource.entry.resource.ofType(MessageHeader).destination.receiver.reference.resolve() or Bundle.entry.resource.ofType(Communication).recipient.exists().not()}medcom-careCommunication-11:If a specific sender is present, at least one of the organisations that the
  referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.sender.
 If no specific sender extension is present, this rule is not evaluated. {Bundle.entry.resource.ofType(Communication).extension.value.reference.resolve().managingOrganization.reference.resolve()

--- a/ig/carecommunication/all-profiles.xlsx
+++ b/ig/carecommunication/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.2</t>
+    <t>5.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T11:55:29+00:00</t>
+    <t>2026-06-03T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2679,7 +2679,7 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 medcom-carecommunication-definition-url:SHALL reference a MedCom CareCommunication MessageDefinition whose canonical URL starts with
-http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5. — that is, any version 5.x of the message definition. The current minor version the sender uses must be added in the end of the definition. {matches('^http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5[.][0-9]{1,2}$')}</t>
+http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5. — that is, any version 5.x of the message definition. The current minor version the sender uses must be added in the end of the definition. {matches('^http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition[|]5[.][0-9]{1,2}$')}</t>
   </si>
   <si>
     <t>medcom-careCommunication-provenance</t>

--- a/ig/carecommunication/all-profiles.xlsx
+++ b/ig/carecommunication/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.3</t>
+    <t>5.0.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:32:39+00:00</t>
+    <t>2026-06-05T08:11:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}medcom-careCommunication-5:Priority must not be present when Communication.category is other than 'regarding-referral' {where(category.coding.code != 'regarding-referral').priority.empty()}medcom-careCommunication-6:There shall exist a Communication.topic when Communication.category = 'other' {iif(category.coding.code != 'other', true, category.coding.code = 'other' and topic.exists())}medcom-careCommunication-7:There shall exist a practitioner role when using a PractitionerRole as author in a message segment. {payload.extension('http://medcomfhir.dk/ig/core/StructureDefinition/medcom-core-practitioner-extension').value.resolve().all(code.coding.code.exists() xor code.text.exists())}medcom-careCommunication-8:There shall exist a practitioner name when using a Practitioner as author in a message segment. {payload.where(extension('http://medcomfhir.dk/ig/core/StructureDefinition/medcom-core-practitioner-extension').exists()).extension.value.reference.resolve().practitioner.resolve().name.exists()}medcom-careCommunication-9:An episodeOfCare-identifier must be included when an Encounter instance is included. {iif(encounter.exists().not(), true, encounter.reference.resolve().episodeOfCare.identifier.exists())}medcom-careCommunication-15:If an Encounter resource is present in the bundle, there must be a reference to it in Communication.encounter. If no Encounter is present, Communication.encounter must not be populated. {iif(encounter.exists(), Communication.encounter.reference.exists(), Communication.encounter.exists().not())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}medcom-careCommunication-5:Priority must not be present when Communication.category is other than 'regarding-referral' {where(category.coding.code != 'regarding-referral').priority.empty()}medcom-careCommunication-6:There shall exist a Communication.topic when Communication.category = 'other' {iif(category.coding.code != 'other', true, category.coding.code = 'other' and topic.exists())}medcom-careCommunication-7:There shall exist a practitioner role when using a PractitionerRole as author in a message segment. {payload.extension('http://medcomfhir.dk/ig/core/StructureDefinition/medcom-core-practitioner-extension').value.resolve().all(code.coding.code.exists() xor code.text.exists())}medcom-careCommunication-8:There shall exist a practitioner name when using a Practitioner as author in a message segment. {payload.where(extension('http://medcomfhir.dk/ig/core/StructureDefinition/medcom-core-practitioner-extension').exists()).extension.value.reference.resolve().practitioner.resolve().name.exists()}medcom-careCommunication-9:An episodeOfCare-identifier must be included when an Encounter instance is included. {iif(encounter.exists().not(), true, encounter.reference.resolve().episodeOfCare.identifier.exists())}</t>
   </si>
   <si>
     <t>Communication.id</t>
@@ -1594,7 +1594,9 @@
         = %resource.entry.resource.ofType(MessageHeader).sender.reference.resolve()
     or Bundle.entry.resource.ofType(Communication).extension.value.reference.resolve().organization.reference.resolve()
         = %resource.entry.resource.ofType(MessageHeader).sender.reference.resolve()
-    or Bundle.entry.resource.ofType(Communication).extension.exists().not()}medcom-careCommunication-13:All PractitionerRole resources shall have a reference to an instance of a Practitioner resource. {Bundle.entry.resource.ofType(PractitionerRole).practitioner.reference.exists()}</t>
+    or Bundle.entry.resource.ofType(Communication).extension.exists().not()}medcom-careCommunication-13:All PractitionerRole resources shall have a reference to an instance of a Practitioner resource. {Bundle.entry.resource.ofType(PractitionerRole).practitioner.reference.exists()}medcom-careCommunication-15:If an Encounter resource is present in the bundle, there must be a reference to it in Communication.encounter. If no Encounter is present, Communication.encounter must not be populated. {iif(Bundle.entry.resource.ofType(Encounter).exists(),
+                Bundle.entry.resource.ofType(Encounter).id = Bundle.entry.resource.ofType(Communication).encounter.reference.resolve().id,
+                Bundle.entry.resource.ofType(Communication).encounter.exists().not())}</t>
   </si>
   <si>
     <t>Bundle.id</t>
